--- a/results/components/gene_names/p3s7.xlsx
+++ b/results/components/gene_names/p3s7.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
   <si>
     <t>gene1</t>
   </si>
@@ -22,166 +22,187 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Psn</t>
-  </si>
-  <si>
-    <t>Ark</t>
-  </si>
-  <si>
-    <t>sle</t>
-  </si>
-  <si>
-    <t>tral</t>
-  </si>
-  <si>
-    <t>Aph-4</t>
-  </si>
-  <si>
-    <t>poe</t>
+    <t>Ef1gamma</t>
+  </si>
+  <si>
+    <t>tin</t>
+  </si>
+  <si>
+    <t>MED11</t>
+  </si>
+  <si>
+    <t>Cks30A</t>
+  </si>
+  <si>
+    <t>Rack1</t>
+  </si>
+  <si>
+    <t>Hem</t>
+  </si>
+  <si>
+    <t>sty</t>
+  </si>
+  <si>
+    <t>CG9520</t>
+  </si>
+  <si>
+    <t>Moe</t>
+  </si>
+  <si>
+    <t>Cyt-c-d</t>
+  </si>
+  <si>
+    <t>Set2</t>
+  </si>
+  <si>
+    <t>Pvr</t>
+  </si>
+  <si>
+    <t>l(2)efl</t>
+  </si>
+  <si>
+    <t>tld</t>
+  </si>
+  <si>
+    <t>Pk92B</t>
+  </si>
+  <si>
+    <t>dpp</t>
   </si>
   <si>
     <t>Su(var)2-10</t>
   </si>
   <si>
-    <t>mbl</t>
-  </si>
-  <si>
-    <t>vlc</t>
+    <t>l(3)mbt</t>
+  </si>
+  <si>
+    <t>dei</t>
+  </si>
+  <si>
+    <t>eg</t>
+  </si>
+  <si>
+    <t>sgg</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>Bap60</t>
+  </si>
+  <si>
+    <t>Dat</t>
+  </si>
+  <si>
+    <t>Dif</t>
+  </si>
+  <si>
+    <t>Rca1</t>
   </si>
   <si>
     <t>bon</t>
   </si>
   <si>
-    <t>bnl</t>
-  </si>
-  <si>
-    <t>Ice</t>
+    <t>esc</t>
+  </si>
+  <si>
+    <t>SelD</t>
+  </si>
+  <si>
+    <t>CkIIalpha</t>
+  </si>
+  <si>
+    <t>sas</t>
+  </si>
+  <si>
+    <t>spen</t>
+  </si>
+  <si>
+    <t>lmd</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>hpo</t>
+  </si>
+  <si>
+    <t>Eip63E</t>
+  </si>
+  <si>
+    <t>abd-A</t>
+  </si>
+  <si>
+    <t>dnc</t>
+  </si>
+  <si>
+    <t>eff</t>
+  </si>
+  <si>
+    <t>SelG</t>
+  </si>
+  <si>
+    <t>cnc</t>
+  </si>
+  <si>
+    <t>glu</t>
+  </si>
+  <si>
+    <t>numb</t>
+  </si>
+  <si>
+    <t>Idgf4</t>
+  </si>
+  <si>
+    <t>how</t>
+  </si>
+  <si>
+    <t>Dad</t>
+  </si>
+  <si>
+    <t>foxo</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>Lac</t>
+  </si>
+  <si>
+    <t>kis</t>
+  </si>
+  <si>
+    <t>Sry-delta</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>Tm1</t>
+  </si>
+  <si>
+    <t>chic</t>
+  </si>
+  <si>
+    <t>Sb</t>
+  </si>
+  <si>
+    <t>Pgant35A</t>
+  </si>
+  <si>
+    <t>ine</t>
+  </si>
+  <si>
+    <t>Yp1</t>
   </si>
   <si>
     <t>rdo</t>
   </si>
   <si>
-    <t>cort</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>rux</t>
-  </si>
-  <si>
-    <t>aft</t>
-  </si>
-  <si>
-    <t>cher</t>
-  </si>
-  <si>
-    <t>loco</t>
+    <t>trc</t>
   </si>
   <si>
     <t>18w</t>
-  </si>
-  <si>
-    <t>Cks30A</t>
-  </si>
-  <si>
-    <t>Lis-1</t>
-  </si>
-  <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>Tak1</t>
-  </si>
-  <si>
-    <t>Mitf</t>
-  </si>
-  <si>
-    <t>mask</t>
-  </si>
-  <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>thr</t>
-  </si>
-  <si>
-    <t>ttk</t>
-  </si>
-  <si>
-    <t>ALiX</t>
-  </si>
-  <si>
-    <t>CG6416</t>
-  </si>
-  <si>
-    <t>CG9509</t>
-  </si>
-  <si>
-    <t>Idgf2</t>
-  </si>
-  <si>
-    <t>drm</t>
-  </si>
-  <si>
-    <t>Oseg1</t>
-  </si>
-  <si>
-    <t>Syx1A</t>
-  </si>
-  <si>
-    <t>pyd</t>
-  </si>
-  <si>
-    <t>wal</t>
-  </si>
-  <si>
-    <t>Pak</t>
-  </si>
-  <si>
-    <t>dnc</t>
-  </si>
-  <si>
-    <t>dl</t>
-  </si>
-  <si>
-    <t>fal</t>
-  </si>
-  <si>
-    <t>Caf1</t>
-  </si>
-  <si>
-    <t>sktl</t>
-  </si>
-  <si>
-    <t>eff</t>
-  </si>
-  <si>
-    <t>Fas3</t>
-  </si>
-  <si>
-    <t>odd</t>
-  </si>
-  <si>
-    <t>emb</t>
-  </si>
-  <si>
-    <t>FKBP59</t>
-  </si>
-  <si>
-    <t>cas</t>
-  </si>
-  <si>
-    <t>E2f</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>dmt</t>
-  </si>
-  <si>
-    <t>pot</t>
   </si>
 </sst>
 </file>
@@ -513,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -662,90 +683,122 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
         <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
         <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" t="s">
         <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s">
         <v>49</v>
-      </c>
-      <c r="B26" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
         <v>50</v>
-      </c>
-      <c r="B27" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s">
         <v>52</v>
-      </c>
-      <c r="B28" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
         <v>54</v>
       </c>
-      <c r="B29" t="s">
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
         <v>55</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
